--- a/docs/reports/Test_Cases_EvMoto_Mobile_EN.xlsx
+++ b/docs/reports/Test_Cases_EvMoto_Mobile_EN.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Driver" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin Dashboard" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User'!$A$1:$I$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Admin Dashboard'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13608,6 +13610,1111 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId299"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>300</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="300" name="Image 300" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId300"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>301</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="301" name="Image 301" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId301"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>302</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="302" name="Image 302" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId302"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>303</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="303" name="Image 303" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId303"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>304</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="304" name="Image 304" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId304"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>305</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="305" name="Image 305" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId305"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>306</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="306" name="Image 306" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId306"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>307</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="307" name="Image 307" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId307"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>308</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="308" name="Image 308" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId308"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>309</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="309" name="Image 309" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId309"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>310</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="310" name="Image 310" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId310"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>311</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="311" name="Image 311" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId311"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="312" name="Image 312" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId312"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>313</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="313" name="Image 313" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId313"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>314</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="314" name="Image 314" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId314"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>315</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="315" name="Image 315" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId315"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>316</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="316" name="Image 316" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId316"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>317</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="317" name="Image 317" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId317"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>318</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="318" name="Image 318" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId318"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>319</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="319" name="Image 319" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId319"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>320</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="320" name="Image 320" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId320"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>321</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="321" name="Image 321" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId321"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>322</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="322" name="Image 322" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId322"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>323</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="323" name="Image 323" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId323"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>324</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="324" name="Image 324" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId324"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>325</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="325" name="Image 325" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId325"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>326</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="326" name="Image 326" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId326"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>327</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="327" name="Image 327" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId327"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -24712,7 +25819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -36292,7 +37399,7 @@
     <row r="284" ht="135" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>TC_DRV_RENT_PT_01</t>
+          <t>TC_DRV_BOOK_BG_01</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr"/>
@@ -36303,674 +37410,2641 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
+          <t>EvMoto Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) active on Dev Golang (https://evmotodev.justkidding.app). Driver is Online on Home Dashboard ready for dispatch.</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Online dan smartphone dalam kondisi standby background / membuka aplikasi lain
+2. Backend mem-broadcast Order baru (Order EVMoto Motor) dengan durasi bidding window 20 detik
+3. Driver membuka Screen smartphone setelah jeda 5 detik standby
+4. Driver melakukan swipe/swap untuk Accept Order sebelum timer habis</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>Pop-up overlay tidak lenyap prematur dalam 3-5 detik, swipe terima orderan Successful mengunci Order.</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr"/>
+      <c r="H284" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 on Dev Golang. Base fare, 10% platform fee, waiting fee, coupon subsidy, 2% surcharge, and cancellation penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="135" customHeight="1">
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_02</t>
+        </is>
+      </c>
+      <c r="B285" s="8" t="inlineStr"/>
+      <c r="C285" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D285" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) active on Dev Golang (https://evmotodev.justkidding.app). Driver is Online on Home Dashboard ready for dispatch.</t>
+        </is>
+      </c>
+      <c r="E285" s="8" t="inlineStr">
+        <is>
+          <t>1. Smartphone driver terkunci dalam mode Screen mati (Deep Sleep / Screen OFF)
+2. Order masuk diterima oleh BackgroundService driver saat Screen mati
+3. Sistem wajib memvalidasi ketersediaan WakeLock dan Full-Screen Intent
+4. Grace Window Guard aktif: driver diberikan minimal 15 detik window efektif sejak Screen ON</t>
+        </is>
+      </c>
+      <c r="F285" s="8" t="inlineStr">
+        <is>
+          <t>Sistem mencegah hangusnya window penawaran secara prematur (mencegah bug pop-up 3-5 detik lenyap).</t>
+        </is>
+      </c>
+      <c r="G285" s="10" t="inlineStr"/>
+      <c r="H285" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I285" s="8" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 on Dev Golang. Base fare, 10% platform fee, waiting fee, coupon subsidy, 2% surcharge, and cancellation penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="135" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_03</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr"/>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) active on Dev Golang (https://evmotodev.justkidding.app). Driver is Online on Home Dashboard ready for dispatch.</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>1. Order di-broadcast ke beberapa driver di sekitar lokasi penjemputan
+2. Driver B lebih cepat melakukan swipe/swap Accept orderan di detik ke-6
+3. Sistem mengirimkan event notifikasi pembatalan penawaran ke Driver A yang baru membuka Screen
+4. Aplikasi Driver A menampilkan feedback transisi visual sebelum menutup overlay</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>Muncul feedback visual yang jelas dan sopan kepada driver, bukan pop-up yang mendadak lenyap tanpa jejak.</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr"/>
+      <c r="H286" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 on Dev Golang. Base fare, 10% platform fee, waiting fee, coupon subsidy, 2% surcharge, and cancellation penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="135" customHeight="1">
+      <c r="A287" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BOOK_BG_04</t>
+        </is>
+      </c>
+      <c r="B287" s="8" t="inlineStr"/>
+      <c r="C287" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D287" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver (82283737237 / PIN 1234) &amp; User (82146625856 / PIN 1234) active on Dev Golang (https://evmotodev.justkidding.app). Driver is Online on Home Dashboard ready for dispatch.</t>
+        </is>
+      </c>
+      <c r="E287" s="8" t="inlineStr">
+        <is>
+          <t>1. Aplikasi berjalan di latar belakang dan floating overlay window sedang aktif
+2. User membuka aplikasi dan memicu transisi AppLifecycleState: paused -&gt; resumed
+3. Sistem mempertahankan integritas floating window tanpa memicu closeOrderOverlay() prematur
+4. Overlay window tetap terpasang pada WindowManager Android hingga user swipe atau timeout habis</t>
+        </is>
+      </c>
+      <c r="F287" s="8" t="inlineStr">
+        <is>
+          <t>Overlay tetap stabil dan tidak ter-destroy akibat transisi window manager Android.</t>
+        </is>
+      </c>
+      <c r="G287" s="10" t="inlineStr"/>
+      <c r="H287" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I287" s="8" t="inlineStr">
+        <is>
+          <t>Driver Booking &amp; Pricing Engine: Driver 82283737237, User 82146625856, PIN bypass 1234 on Dev Golang. Base fare, 10% platform fee, waiting fee, coupon subsidy, 2% surcharge, and cancellation penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="135" customHeight="1">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_RENT_PT_01</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr"/>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E284" s="3" t="inlineStr">
+      <c r="E288" s="3" t="inlineStr">
         <is>
           <t>1. Driver baru (Fresh Driver) masuk ke menu Manajemen Kendaraan
 2. Status kendaraan menampilkan empty state belum memiliki kendaraan terdaftar
 3. Status toggle 'Hubungkan Akun' berada pada kondisi OFF (Belum Terhubung)</t>
         </is>
       </c>
-      <c r="F284" s="3" t="inlineStr">
+      <c r="F288" s="3" t="inlineStr">
         <is>
           <t>Displayed 'Saat ini belum tersedia kendaraan' dan toggle sakelar berada pada posisi mati (OFF).</t>
         </is>
       </c>
-      <c r="G284" s="5" t="inlineStr"/>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I284" s="3" t="inlineStr">
+      <c r="G288" s="5" t="inlineStr"/>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="285" ht="135" customHeight="1">
-      <c r="A285" s="7" t="inlineStr">
+    <row r="289" ht="135" customHeight="1">
+      <c r="A289" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_02</t>
         </is>
       </c>
-      <c r="B285" s="8" t="inlineStr"/>
-      <c r="C285" s="9" t="inlineStr">
+      <c r="B289" s="8" t="inlineStr"/>
+      <c r="C289" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D285" s="8" t="inlineStr">
+      <c r="D289" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E285" s="8" t="inlineStr">
+      <c r="E289" s="8" t="inlineStr">
         <is>
           <t>1. Existing driver tanpa motor membuka menu penautan armada ECGO
 2. Sistem mengonfirmasi status 'Successful Di Hubungkan' pada modul Super Apps</t>
         </is>
       </c>
-      <c r="F285" s="8" t="inlineStr">
+      <c r="F289" s="8" t="inlineStr">
         <is>
           <t>Unit motor sewa terhubung dan toggle berubah menjadi aktif (Terhubung).</t>
         </is>
       </c>
-      <c r="G285" s="10" t="inlineStr"/>
-      <c r="H285" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I285" s="8" t="inlineStr">
+      <c r="G289" s="10" t="inlineStr"/>
+      <c r="H289" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I289" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="286" ht="135" customHeight="1">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="290" ht="135" customHeight="1">
+      <c r="A290" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_03</t>
         </is>
       </c>
-      <c r="B286" s="3" t="inlineStr"/>
-      <c r="C286" s="4" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr"/>
+      <c r="C290" s="4" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D286" s="3" t="inlineStr">
+      <c r="D290" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E286" s="3" t="inlineStr">
+      <c r="E290" s="3" t="inlineStr">
         <is>
           <t>1. Kontrak Orphan Motor terverifikasi: unit lama tidak di-soft delete dan status backend menjadi 'ORPHAN'</t>
         </is>
       </c>
-      <c r="F286" s="3" t="inlineStr">
+      <c r="F290" s="3" t="inlineStr">
         <is>
           <t>Motor lama berstatus Orphan (tidak dihapus) dan plat nomor baru aktif di akun driver.</t>
         </is>
       </c>
-      <c r="G286" s="5" t="inlineStr"/>
-      <c r="H286" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I286" s="3" t="inlineStr">
+      <c r="G290" s="5" t="inlineStr"/>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="135" customHeight="1">
-      <c r="A287" s="7" t="inlineStr">
+    <row r="291" ht="135" customHeight="1">
+      <c r="A291" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_04</t>
         </is>
       </c>
-      <c r="B287" s="8" t="inlineStr"/>
-      <c r="C287" s="9" t="inlineStr">
+      <c r="B291" s="8" t="inlineStr"/>
+      <c r="C291" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D287" s="8" t="inlineStr">
+      <c r="D291" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E287" s="8" t="inlineStr">
+      <c r="E291" s="8" t="inlineStr">
         <is>
           <t>1. Driver mengaktifkan integrasi akun cicilan sewa pada unit yang sama
 2. Status akun terhubung dengan kontrak cicilan ECGO tanpa mengubah nomor plat aktif</t>
         </is>
       </c>
-      <c r="F287" s="8" t="inlineStr">
+      <c r="F291" s="8" t="inlineStr">
         <is>
           <t>Penautan program cicilan Successful tanpa mengubah data kendaraan aktif.</t>
         </is>
       </c>
-      <c r="G287" s="10" t="inlineStr"/>
-      <c r="H287" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I287" s="8" t="inlineStr">
+      <c r="G291" s="10" t="inlineStr"/>
+      <c r="H291" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I291" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="135" customHeight="1">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="292" ht="135" customHeight="1">
+      <c r="A292" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_05</t>
         </is>
       </c>
-      <c r="B288" s="3" t="inlineStr"/>
-      <c r="C288" s="4" t="inlineStr">
+      <c r="B292" s="3" t="inlineStr"/>
+      <c r="C292" s="4" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D288" s="3" t="inlineStr">
+      <c r="D292" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E288" s="3" t="inlineStr">
+      <c r="E292" s="3" t="inlineStr">
         <is>
           <t>1. Unit Orphan dapat dialihkan dan History kepemilikan sebelumnya tetap tersimpan utuh</t>
         </is>
       </c>
-      <c r="F288" s="3" t="inlineStr">
+      <c r="F292" s="3" t="inlineStr">
         <is>
           <t>Unit Orphan Successful di-reassign ke mitra baru tanpa kehilangan History armada sebelumnya.</t>
         </is>
       </c>
-      <c r="G288" s="5" t="inlineStr"/>
-      <c r="H288" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I288" s="3" t="inlineStr">
+      <c r="G292" s="5" t="inlineStr"/>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="135" customHeight="1">
-      <c r="A289" s="7" t="inlineStr">
+    <row r="293" ht="135" customHeight="1">
+      <c r="A293" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_PT_06</t>
         </is>
       </c>
-      <c r="B289" s="8" t="inlineStr"/>
-      <c r="C289" s="9" t="inlineStr">
+      <c r="B293" s="8" t="inlineStr"/>
+      <c r="C293" s="9" t="inlineStr">
         <is>
           <t>Positive True</t>
         </is>
       </c>
-      <c r="D289" s="8" t="inlineStr">
+      <c r="D293" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E289" s="8" t="inlineStr">
+      <c r="E293" s="8" t="inlineStr">
         <is>
           <t>1. Akun driver telah terhubung (Toggle Status = ON)
 2. Driver mencoba mengetuk switch toggle untuk memutus hubungan akun secara sepihak
 3. Sistem menegakkan aturan One-Way Binding: Sakelar terkunci atau dialog restriksi administrator ditampilkan</t>
         </is>
       </c>
-      <c r="F289" s="8" t="inlineStr">
+      <c r="F293" s="8" t="inlineStr">
         <is>
           <t>Switch berada dalam status disabled/locked, dan upaya klik menampilkan dialog pencegahan pemutusan sepihak.</t>
         </is>
       </c>
-      <c r="G289" s="10" t="inlineStr"/>
-      <c r="H289" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I289" s="8" t="inlineStr">
+      <c r="G293" s="10" t="inlineStr"/>
+      <c r="H293" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I293" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="135" customHeight="1">
-      <c r="A290" s="2" t="inlineStr">
+    <row r="294" ht="135" customHeight="1">
+      <c r="A294" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_01</t>
         </is>
       </c>
-      <c r="B290" s="3" t="inlineStr"/>
-      <c r="C290" s="4" t="inlineStr">
+      <c r="B294" s="3" t="inlineStr"/>
+      <c r="C294" s="4" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D290" s="3" t="inlineStr">
+      <c r="D294" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E290" s="3" t="inlineStr">
+      <c r="E294" s="3" t="inlineStr">
         <is>
           <t>1. Driver menginisiasi proses linking akun
 2. State UI melakukan rollback otomatis ke posisi OFF untuk mencegah desinkronisasi data</t>
         </is>
       </c>
-      <c r="F290" s="3" t="inlineStr">
+      <c r="F294" s="3" t="inlineStr">
         <is>
           <t>Status toggle dikembalikan ke posisi OFF dan Balance tidak mengalami pemotongan sepihak.</t>
         </is>
       </c>
-      <c r="G290" s="5" t="inlineStr"/>
-      <c r="H290" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr"/>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="291" ht="135" customHeight="1">
-      <c r="A291" s="7" t="inlineStr">
+    <row r="295" ht="135" customHeight="1">
+      <c r="A295" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_02</t>
         </is>
       </c>
-      <c r="B291" s="8" t="inlineStr"/>
-      <c r="C291" s="9" t="inlineStr">
+      <c r="B295" s="8" t="inlineStr"/>
+      <c r="C295" s="9" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D291" s="8" t="inlineStr">
+      <c r="D295" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E291" s="8" t="inlineStr">
+      <c r="E295" s="8" t="inlineStr">
         <is>
           <t>1. Sistem memverifikasi integritas basis data kendaraan dan History odometer
 2. History Order masa lalu tersimpan rapi dan log kilometer terus bersambung</t>
         </is>
       </c>
-      <c r="F291" s="8" t="inlineStr">
+      <c r="F295" s="8" t="inlineStr">
         <is>
           <t>Data odometer dan order history unit tidak mengalami data corruption atau override.</t>
         </is>
       </c>
-      <c r="G291" s="10" t="inlineStr"/>
-      <c r="H291" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I291" s="8" t="inlineStr">
+      <c r="G295" s="10" t="inlineStr"/>
+      <c r="H295" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I295" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="292" ht="135" customHeight="1">
-      <c r="A292" s="2" t="inlineStr">
+    <row r="296" ht="135" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_BL_03</t>
         </is>
       </c>
-      <c r="B292" s="3" t="inlineStr"/>
-      <c r="C292" s="4" t="inlineStr">
+      <c r="B296" s="3" t="inlineStr"/>
+      <c r="C296" s="4" t="inlineStr">
         <is>
           <t>Business Logic</t>
         </is>
       </c>
-      <c r="D292" s="3" t="inlineStr">
+      <c r="D296" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E292" s="3" t="inlineStr">
+      <c r="E296" s="3" t="inlineStr">
         <is>
           <t>1. Akun driver aktif dihubungkan pada perangkat utama
 2. Status toggle di perangkat sekunder ter-sinkronisasi realtime dalam posisi ON dan terkunci</t>
         </is>
       </c>
-      <c r="F292" s="3" t="inlineStr">
+      <c r="F296" s="3" t="inlineStr">
         <is>
           <t>Perangkat sekunder langsung menampilkan status ON/Terkunci tanpa inkonsistensi cache lokal.</t>
         </is>
       </c>
-      <c r="G292" s="5" t="inlineStr"/>
-      <c r="H292" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
+      <c r="G296" s="5" t="inlineStr"/>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="135" customHeight="1">
-      <c r="A293" s="7" t="inlineStr">
+    <row r="297" ht="135" customHeight="1">
+      <c r="A297" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_01</t>
         </is>
       </c>
-      <c r="B293" s="8" t="inlineStr"/>
-      <c r="C293" s="9" t="inlineStr">
+      <c r="B297" s="8" t="inlineStr"/>
+      <c r="C297" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D293" s="8" t="inlineStr">
+      <c r="D297" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E293" s="8" t="inlineStr">
+      <c r="E297" s="8" t="inlineStr">
         <is>
           <t>1. Permintaan pemutusan koneksi sepihak dikirim tanpa otorisasi Superadmin</t>
         </is>
       </c>
-      <c r="F293" s="8" t="inlineStr">
+      <c r="F297" s="8" t="inlineStr">
         <is>
           <t>Backend Reject request dengan status HTTP 403 Forbidden (kebijakan One-Way Binding ditegakkan).</t>
         </is>
       </c>
-      <c r="G293" s="10" t="inlineStr"/>
-      <c r="H293" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I293" s="8" t="inlineStr">
+      <c r="G297" s="10" t="inlineStr"/>
+      <c r="H297" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I297" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="135" customHeight="1">
-      <c r="A294" s="2" t="inlineStr">
+    <row r="298" ht="135" customHeight="1">
+      <c r="A298" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_02</t>
         </is>
       </c>
-      <c r="B294" s="3" t="inlineStr"/>
-      <c r="C294" s="4" t="inlineStr">
+      <c r="B298" s="3" t="inlineStr"/>
+      <c r="C298" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D294" s="3" t="inlineStr">
+      <c r="D298" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E294" s="3" t="inlineStr">
+      <c r="E298" s="3" t="inlineStr">
         <is>
           <t>1. Sistem anti-fraud Reject penautan duplikat dan menampilkan peringatan konflik armada</t>
         </is>
       </c>
-      <c r="F294" s="3" t="inlineStr">
+      <c r="F298" s="3" t="inlineStr">
         <is>
           <t>Muncul notifikasi penolakan 'Kendaraan sedang digunakan oleh driver aktif lain'.</t>
         </is>
       </c>
-      <c r="G294" s="5" t="inlineStr"/>
-      <c r="H294" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I294" s="3" t="inlineStr">
+      <c r="G298" s="5" t="inlineStr"/>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I298" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="295" ht="135" customHeight="1">
-      <c r="A295" s="7" t="inlineStr">
+    <row r="299" ht="135" customHeight="1">
+      <c r="A299" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NF_03</t>
         </is>
       </c>
-      <c r="B295" s="8" t="inlineStr"/>
-      <c r="C295" s="9" t="inlineStr">
+      <c r="B299" s="8" t="inlineStr"/>
+      <c r="C299" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D295" s="8" t="inlineStr">
+      <c r="D299" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E295" s="8" t="inlineStr">
+      <c r="E299" s="8" t="inlineStr">
         <is>
           <t>1. Driver telah melepas motor lama menjadi unit berstatus Orphan
 2. Akses telemetri dibatasi sepenuhnya dan kontrol berpindah ke sistem sentral</t>
         </is>
       </c>
-      <c r="F295" s="8" t="inlineStr">
+      <c r="F299" s="8" t="inlineStr">
         <is>
           <t>Akses ditolak dan token telemetri kendaraan lama otomatis dicabut (revoked).</t>
         </is>
       </c>
-      <c r="G295" s="10" t="inlineStr"/>
-      <c r="H295" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I295" s="8" t="inlineStr">
+      <c r="G299" s="10" t="inlineStr"/>
+      <c r="H299" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I299" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="296" ht="135" customHeight="1">
-      <c r="A296" s="2" t="inlineStr">
+    <row r="300" ht="135" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_01</t>
         </is>
       </c>
-      <c r="B296" s="3" t="inlineStr"/>
-      <c r="C296" s="4" t="inlineStr">
+      <c r="B300" s="3" t="inlineStr"/>
+      <c r="C300" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D296" s="3" t="inlineStr">
+      <c r="D300" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E296" s="3" t="inlineStr">
+      <c r="E300" s="3" t="inlineStr">
         <is>
           <t>1. Motor mitra mengalami kerusakan teknis darurat dan ditukar di bengkel resmi ECGO
 2. Mekanik mengesahkan berita acara pertukaran unit fisik di portal operasional
 3. Aplikasi Driver menyerap identitas unit baru secara otomatis tanpa membatalkan cicilan</t>
         </is>
       </c>
-      <c r="F296" s="3" t="inlineStr">
+      <c r="F300" s="3" t="inlineStr">
         <is>
           <t>Unit pengganti terhubung secara otomatis ke kontrak sewa aktif driver.</t>
         </is>
       </c>
-      <c r="G296" s="5" t="inlineStr"/>
-      <c r="H296" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I296" s="3" t="inlineStr">
+      <c r="G300" s="5" t="inlineStr"/>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I300" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="135" customHeight="1">
-      <c r="A297" s="7" t="inlineStr">
+    <row r="301" ht="135" customHeight="1">
+      <c r="A301" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_02</t>
         </is>
       </c>
-      <c r="B297" s="8" t="inlineStr"/>
-      <c r="C297" s="9" t="inlineStr">
+      <c r="B301" s="8" t="inlineStr"/>
+      <c r="C301" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D297" s="8" t="inlineStr">
+      <c r="D301" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E297" s="8" t="inlineStr">
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>1. Driver mengklik sakelar Hubungkan Akun
 2. Aplikasi menampilkan pesan timeout ramah User dan opsi coba kembali tanpa error crash</t>
         </is>
       </c>
-      <c r="F297" s="8" t="inlineStr">
+      <c r="F301" s="8" t="inlineStr">
         <is>
           <t>Sistem menyajikan Button 'Coba Lagi' tanpa menduplikasi data transaksi di backend.</t>
         </is>
       </c>
-      <c r="G297" s="10" t="inlineStr"/>
-      <c r="H297" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I297" s="8" t="inlineStr">
+      <c r="G301" s="10" t="inlineStr"/>
+      <c r="H301" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="135" customHeight="1">
-      <c r="A298" s="2" t="inlineStr">
+    <row r="302" ht="135" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_03</t>
         </is>
       </c>
-      <c r="B298" s="3" t="inlineStr"/>
-      <c r="C298" s="4" t="inlineStr">
+      <c r="B302" s="3" t="inlineStr"/>
+      <c r="C302" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D298" s="3" t="inlineStr">
+      <c r="D302" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E298" s="3" t="inlineStr">
+      <c r="E302" s="3" t="inlineStr">
         <is>
           <t>1. Driver belum mengaktifkan penautan akun cicilan (Status Unlinked)
 2. Driver mengakses menu aktivitas, dompet reguler, dan panduan pengemudi
 3. Aplikasi tetap berfungsi penuh dengan menampilkan kartu edukasi manfaat penautan armada</t>
         </is>
       </c>
-      <c r="F298" s="3" t="inlineStr">
+      <c r="F302" s="3" t="inlineStr">
         <is>
           <t>Aplikasi berjalan mulus dengan banner pengingat penautan akun tanpa memblokir operasional normal.</t>
         </is>
       </c>
-      <c r="G298" s="5" t="inlineStr"/>
-      <c r="H298" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
+      <c r="G302" s="5" t="inlineStr"/>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I302" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="135" customHeight="1">
-      <c r="A299" s="7" t="inlineStr">
+    <row r="303" ht="135" customHeight="1">
+      <c r="A303" s="7" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_04</t>
         </is>
       </c>
-      <c r="B299" s="8" t="inlineStr"/>
-      <c r="C299" s="9" t="inlineStr">
+      <c r="B303" s="8" t="inlineStr"/>
+      <c r="C303" s="9" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D299" s="8" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E299" s="8" t="inlineStr">
+      <c r="E303" s="8" t="inlineStr">
         <is>
           <t>1. Driver memicu proses Verify data kontrak sewa motor
 2. Sistem Reject penautan otomatis demi keamanan identitas dan pencegahan pemalsuan data</t>
         </is>
       </c>
-      <c r="F299" s="8" t="inlineStr">
+      <c r="F303" s="8" t="inlineStr">
         <is>
           <t>Penautan dibatalkan dan sistem meminta driver melakukan Verify KTP di kantor cabang.</t>
         </is>
       </c>
-      <c r="G299" s="10" t="inlineStr"/>
-      <c r="H299" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I299" s="8" t="inlineStr">
+      <c r="G303" s="10" t="inlineStr"/>
+      <c r="H303" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I303" s="8" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="135" customHeight="1">
-      <c r="A300" s="2" t="inlineStr">
+    <row r="304" ht="135" customHeight="1">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>TC_DRV_RENT_NT_05</t>
         </is>
       </c>
-      <c r="B300" s="3" t="inlineStr"/>
-      <c r="C300" s="4" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr"/>
+      <c r="C304" s="4" t="inlineStr">
         <is>
           <t>Negative True</t>
         </is>
       </c>
-      <c r="D300" s="3" t="inlineStr">
+      <c r="D304" s="3" t="inlineStr">
         <is>
           <t>User is on the active application screen</t>
         </is>
       </c>
-      <c r="E300" s="3" t="inlineStr">
+      <c r="E304" s="3" t="inlineStr">
         <is>
           <t>1. Driver mencoba memindai QR code stasiun swap baterai ECGO di tengah jalan
 2. Sistem memblokir proses swap dan menginstruksikan driver mengantar penumpang ke tujuan terlebih dahulu</t>
         </is>
       </c>
-      <c r="F300" s="3" t="inlineStr">
+      <c r="F304" s="3" t="inlineStr">
         <is>
           <t>Muncul dialog peringatan untuk menyelesaikan Order terlebih dahulu sebelum melakukan penukaran baterai.</t>
         </is>
       </c>
-      <c r="G300" s="5" t="inlineStr"/>
-      <c r="H300" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I300" s="3" t="inlineStr">
+      <c r="G304" s="5" t="inlineStr"/>
+      <c r="H304" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I304" s="3" t="inlineStr">
         <is>
           <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
         </is>
       </c>
     </row>
+    <row r="305" ht="135" customHeight="1">
+      <c r="A305" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_01</t>
+        </is>
+      </c>
+      <c r="B305" s="8" t="inlineStr"/>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>1. Server mendispatch 3 order dalam satu batch ke aplikasi driver
+2. Aplikasi Driver menampilkan 3 tawaran order secara simultan</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver menampilkan seluruh kartu order dalam daftar (misal 3 order simultan) dengan rincian titik jemput, titik antar, dan perkiraan pendapatan.</t>
+        </is>
+      </c>
+      <c r="G305" s="10" t="inlineStr"/>
+      <c r="H305" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I305" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="135" customHeight="1">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_02</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr"/>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver Accept tawaran Order dari jalur batch dispatch
+2. Memeriksa indikator timer pada seluruh kartu penawaran order
+3. Kartu order terkonfirmasi TIDAK MEMILIKI countdown timer</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>Field 'has_countdown' bernilai False dan tidak ada hitung mundur pada antarmuka order.</t>
+        </is>
+      </c>
+      <c r="G306" s="5" t="inlineStr"/>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I306" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="135" customHeight="1">
+      <c r="A307" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_03</t>
+        </is>
+      </c>
+      <c r="B307" s="8" t="inlineStr"/>
+      <c r="C307" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D307" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E307" s="8" t="inlineStr">
+        <is>
+          <t>1. Screen menampilkan 2 pilihan order batch yang tersedia
+2. Driver melakukan Swipe/Terima pada order ORD-PICK-A
+3. Order ORD-PICK-A Successful diterima dan menjadi order aktif driver</t>
+        </is>
+      </c>
+      <c r="F307" s="8" t="inlineStr">
+        <is>
+          <t>Order terpilih berpindah ke status 'ACCEPTED', dan siklus penjemputan dimulai.</t>
+        </is>
+      </c>
+      <c r="G307" s="10" t="inlineStr"/>
+      <c r="H307" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I307" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="135" customHeight="1">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PT_04</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr"/>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>1. Batch dispatch mengirimkan kombinasi Order reguler dan terjadwal
+2. Memeriksa kategorisasi tipe order pada daftar
+3. Kedua tipe order terpisah secara kategoris</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>Order berkategori 'regular' ditandai sebagai 'Order Reguler', sedangkan order berkategori 'advance' ditandai sebagai 'Advance Booking' (Order Terjadwal).</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="inlineStr"/>
+      <c r="H308" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I308" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="135" customHeight="1">
+      <c r="A309" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_01</t>
+        </is>
+      </c>
+      <c r="B309" s="8" t="inlineStr"/>
+      <c r="C309" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D309" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E309" s="8" t="inlineStr">
+        <is>
+          <t>1. Batas kapasitas order bersamaan diatur menjadi 3 Order
+2. Driver Accept 3 Order berturut-turut
+3. Driver memegang tepat 3 Order aktif
+4. Upaya Accept Order ke-4 ditolak oleh sistem</t>
+        </is>
+      </c>
+      <c r="F309" s="8" t="inlineStr">
+        <is>
+          <t>Driver sukses memegang 3 order. Upaya Accept order ke-4 ditolak secara valid karena telah mencapai batas concurrent order.</t>
+        </is>
+      </c>
+      <c r="G309" s="10" t="inlineStr"/>
+      <c r="H309" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I309" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="135" customHeight="1">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_02</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr"/>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>1. Tawaran order batch Displayed di Screen
+2. Driver membiarkan tawaran terbuka selama simulasi beberapa waktu
+3. Tawaran order tetap aktif dan siap diambil kapan saja</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="inlineStr">
+        <is>
+          <t>Tawaran order tetap berstatus 'OFFERED' (tidak auto-expire atau menghilang sendiri).</t>
+        </is>
+      </c>
+      <c r="G310" s="5" t="inlineStr"/>
+      <c r="H310" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I310" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="135" customHeight="1">
+      <c r="A311" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_PF_03</t>
+        </is>
+      </c>
+      <c r="B311" s="8" t="inlineStr"/>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver hanya memiliki penawaran Order tipe Reguler
+2. Memfilter daftar berdasarkan tipe 'advance'
+3. Daftar Advance Booking Empty dengan aman</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="inlineStr">
+        <is>
+          <t>Tab Advance Booking menampilkan state Empty secara aman tanpa error ('Belum Ada Order Terjadwal').</t>
+        </is>
+      </c>
+      <c r="G311" s="10" t="inlineStr"/>
+      <c r="H311" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I311" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="135" customHeight="1">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_01</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr"/>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>1. Terdapat 2 order dalam daftar batch
+2. Driver menekan Button 'Tolak' pada ORD-REJECT-ME
+3. Order ORD-REJECT-ME Successful di-reject</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>Order tersebut dihapus dari daftar penawaran aktif driver ('REJECTED'), sedangkan order lain pada batch tetap utuh di Screen.</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="inlineStr"/>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I312" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="135" customHeight="1">
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_02</t>
+        </is>
+      </c>
+      <c r="B313" s="8" t="inlineStr"/>
+      <c r="C313" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver telah Accept order ORD-TO-CANCEL
+2. Driver melakukan pembatalan order dengan alasan resmi
+3. Order terkonfirmasi DIBATALKAN dan slot driver kembali tersedia</t>
+        </is>
+      </c>
+      <c r="F313" s="8" t="inlineStr">
+        <is>
+          <t>Order Successful dibatalkan, status beralih ke 'CANCELLED', dan kapasitas driver kembali pulih.</t>
+        </is>
+      </c>
+      <c r="G313" s="10" t="inlineStr"/>
+      <c r="H313" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I313" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="135" customHeight="1">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_03</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr"/>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-01 disiarkan ke beberapa driver dalam satu batch
+2. Driver lain telah mengklaim order ORD-RACE-01 terlebih dahulu di server
+3. Upaya driver Accept order yang sudah diambil ditolak</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>Sistem Reject konfirmasi penerimaan dan memunculkan banner 'Orderan sudah diambil' ('Semoga lain kali lebih beruntung').</t>
+        </is>
+      </c>
+      <c r="G314" s="5" t="inlineStr"/>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I314" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="135" customHeight="1">
+      <c r="A315" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NT_04</t>
+        </is>
+      </c>
+      <c r="B315" s="8" t="inlineStr"/>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Offline
+2. Server mencoba mendispatch batch order
+3. Broadcast ditolak dan driver tidak Accept tawaran
+4. Upaya Accept order saat offline melempar error</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Reject broadcast ke driver offline dan menghasilkan respons FAILED.</t>
+        </is>
+      </c>
+      <c r="G315" s="10" t="inlineStr"/>
+      <c r="H315" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I315" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="135" customHeight="1">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_01</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr"/>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>Mekanisme thread-safe atomic lock mencegah Order ganda atau duplikasi status trip.</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr"/>
+      <c r="H316" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I316" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="135" customHeight="1">
+      <c r="A317" s="7" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_02</t>
+        </is>
+      </c>
+      <c r="B317" s="8" t="inlineStr"/>
+      <c r="C317" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D317" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E317" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F317" s="8" t="inlineStr">
+        <is>
+          <t>Penolakan kedua tidak menyebabkan crash atau pengecualian tidak tertangani.</t>
+        </is>
+      </c>
+      <c r="G317" s="10" t="inlineStr"/>
+      <c r="H317" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I317" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="135" customHeight="1">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>TC_DRV_BATCH_NF_03</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr"/>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh tawaran multiple order tetap utuh dan tersimpan dalam memory state tanpa data loss.</t>
+        </is>
+      </c>
+      <c r="G318" s="5" t="inlineStr"/>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I318" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto Driver Dev (com.evmoto.driver.app). Pre-order functionality verified stable without active order dispatch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="135" customHeight="1">
+      <c r="A319" s="7" t="inlineStr">
+        <is>
+          <t>TC_VOL_01</t>
+        </is>
+      </c>
+      <c r="B319" s="8" t="inlineStr"/>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver berstatus Online dan siap Accept Order volume tinggi
+2. Server mem-broadcast 8 order batch ke aplikasi driver
+3. Driver sukses Accept dan menampilkan seluruh 8 order</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi Driver mampu memuat dan menampilkan ke-8 order secara bersamaan tanpa lag atau drop data.</t>
+        </is>
+      </c>
+      <c r="G319" s="10" t="inlineStr"/>
+      <c r="H319" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I319" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="135" customHeight="1">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>TC_VOL_02</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr"/>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>1. Sistem memicu lonjakan order di area pusat kota (15 Order masuk)
+2. 15 order disiarkan sekaligus ke Driver
+3. Seluruh 15 order Successful terdaftar di aplikasi driver</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="inlineStr">
+        <is>
+          <t>Sistem memproses ke-15 order secara deterministik, tanpa adanya countdown timer, dan mempertahankan integritas memory state.</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr"/>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I320" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="135" customHeight="1">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>TC_VOL_03</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr"/>
+      <c r="C321" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver Accept daftar batch berisi 8 order
+2. Driver Accept 5 order berturut-turut (mencapai batas concurrent)
+3. Driver memegang tepat 5 order aktif dan status menjadi tidak tersedia
+4. Upaya Accept order ke-6 (ORD-CAP-6) ditolak oleh sistem</t>
+        </is>
+      </c>
+      <c r="F321" s="8" t="inlineStr">
+        <is>
+          <t>Order 1 s/d 5 sukses diterima. Upaya Accept order ke-6 ditolak dengan pesan kapasitas penuh.</t>
+        </is>
+      </c>
+      <c r="G321" s="10" t="inlineStr"/>
+      <c r="H321" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I321" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="135" customHeight="1">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>TC_VOL_04</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr"/>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver memilih dan Accept khusus ORD-TEN-07
+2. Daftar tawaran yang tersisa menyisakan 9 order</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="inlineStr">
+        <is>
+          <t>Hanya order ke-7 yang beralih status ke 'ACCEPTED', 9 order lainnya tetap dalam status 'OFFERED'.</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr"/>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I322" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="135" customHeight="1">
+      <c r="A323" s="7" t="inlineStr">
+        <is>
+          <t>TC_DIST_01</t>
+        </is>
+      </c>
+      <c r="B323" s="8" t="inlineStr"/>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>1. Konfigurasi dashboard memiliki 5 band radius order biasa (0-1, 1-2, 2-3, 3-4, 4-5 km)
+2. Sistem mendispatch seluruh spektrum jarak reguler
+3. Seluruh 5 tingkatan jarak Successful diterima driver secara akurat</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh order dari tiap tingkat jarak Successful diklasifikasikan dan disiarkan dalam batch.</t>
+        </is>
+      </c>
+      <c r="G323" s="10" t="inlineStr"/>
+      <c r="H323" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I323" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="135" customHeight="1">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>TC_DIST_02</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr"/>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto app and navigate through modules sequentially
+2. Verify UI components, buttons, and popup dialogs
+3. Confirm successful execution without application crash</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menangani angka perbatasan secara deterministik tanpa duplikasi atau missing dispatch.</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr"/>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="135" customHeight="1">
+      <c r="A325" s="7" t="inlineStr">
+        <is>
+          <t>TC_DIST_03</t>
+        </is>
+      </c>
+      <c r="B325" s="8" t="inlineStr"/>
+      <c r="C325" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D325" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E325" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto app and navigate through modules sequentially
+2. Verify UI components, buttons, and popup dialogs
+3. Confirm successful execution without application crash</t>
+        </is>
+      </c>
+      <c r="F325" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh Order terjadwal jarak pendek hingga jarak jauh (s/d 15 KM) terakomodasi dalam batch.</t>
+        </is>
+      </c>
+      <c r="G325" s="10" t="inlineStr"/>
+      <c r="H325" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I325" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="135" customHeight="1">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>TC_DIST_04</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr"/>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto app and navigate through modules sequentially
+2. Verify UI components, buttons, and popup dialogs
+3. Confirm successful execution without application crash</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>Sistem menangani Order di luar band radius secara aman (fallback ke sequential atau outer band dispatch) tanpa menyebabkan crash pada pricing engine atau antarmuka driver.</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="inlineStr"/>
+      <c r="H326" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="135" customHeight="1">
+      <c r="A327" s="7" t="inlineStr">
+        <is>
+          <t>TC_E2E_BATCH_01</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr"/>
+      <c r="C327" s="9" t="inlineStr">
+        <is>
+          <t>End-to-End (E2E)</t>
+        </is>
+      </c>
+      <c r="D327" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E327" s="8" t="inlineStr">
+        <is>
+          <t>1. Superadmin mengonfigurasi fitur Dispatch Batch di Dashboard Admin Staging
+2. Sistem menerapkan concurrent limit 5 order ke profil Mitra Driver
+3. Dua Order baru diterbitkan ke sistem dispatching: 1 Reguler (1.8 KM) dan 1 Advance Booking (12.0 KM)
+4. Aplikasi Driver menampilkan 2 tawaran Order secara simultan di Screen
+5. Seluruh tawaran diverifikasi TIDAK MEMILIKI countdown timer
+6. Pemisahan tipe Order terverifikasi tegas (Reguler vs Advance Booking)
+7. Driver Reject (Reject) Order Advance Booking ORD-E2E-ADV-02
+8. Tawaran Advance Booking dikeluarkan dari daftar aktif driver
+9. Driver melakukan Swipe untuk Accept Order Reguler ORD-E2E-REG-01
+10. Driver menjalankan siklus perjalanan hingga selesai
+11. Perjalanan Successful diselesaikan dengan struk pembayaran tunai Rp 12.000</t>
+        </is>
+      </c>
+      <c r="F327" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh siklus terintegrasi Successful 100% tanpa error, tanpa bug, dan konsisten.</t>
+        </is>
+      </c>
+      <c r="G327" s="10" t="inlineStr"/>
+      <c r="H327" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I327" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="135" customHeight="1">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>TC_E2E_BATCH_02</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr"/>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>End-to-End (E2E)</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver Accept satu order baru dari jalur batch
+2. Driver membatalkan Order karena kendala operasional
+3. Order berstatus CANCELLED dan slot driver kembali tersedia</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>Pembatalan terekam dengan Valid dan status driver pulih ke online &amp; standby.</t>
+        </is>
+      </c>
+      <c r="G328" s="5" t="inlineStr"/>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I328" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I300"/>
+  <autoFilter ref="A1:I328"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title / Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pre Condition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Steps to Reproduce</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Current Result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="135" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh komponen UI terdeteksi 100% lengkap dan siap Accept interaksi.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_02</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr"/>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Respons HTTP 200, URL dialihkan ke '?saved=1', dan pesan sukses 'Pengaturan tersimpan.' muncul.</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Kedua daftar jarak tersimpan secara independen tanpa saling menimpa.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="135" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PT_04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Accept konfigurasi mode tanpa batas waktu dan menyimpannya dengan Valid.</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Sistem Successful menyimpan state mati ('enabled=False'). Order berikutnya secara aman fallback ke mode sequential (satu driver per giliran).</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Successful memperbarui daftar band advance booking dengan nilai pengganti baru.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_03</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Kedua nilai batas valid diterima dan disimpan dengan sukses tanpa error 422.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_PF_04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Accept nilai desimal dengan inputmode='decimal' secara presisi.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="135" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_01</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Sistem Reject dengan HTTP 422 Unprocessable Entity dan memunculkan alert spesifik: 'Ukuran batch harus bilangan bulat 1 sampai 50.'</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="135" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_02</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Reject dengan HTTP 422 Unprocessable Entity dan memunculkan alert spesifik: 'Ukuran batch harus bilangan bulat 1 sampai 50.'</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_03</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Sistem Reject masukan korup dengan HTTP 422 dan mencegah perubahan tersimpan di database.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="135" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_04</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Akses ditolak dan diarahkan ke Page login (/login) atau respons 401/302.</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="135" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NT_05</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Sistem Reject dengan HTTP 422 dan pesan alert bisnis: 'Band advance booking yang sudah tersimpan harus diganti dengan daftar baru. Nilai itu tidak bisa dikosongkan.'</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="135" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_01</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Seluruh request diproses secara idempoten (HTTP 200), tidak menyebabkan duplikasi data atau internal server error 500.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="135" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Sistem secara elegan mengabaikan (strip) baris Empty tanpa error atau crash.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="135" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>TC_DASH_BATCH_NF_03</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>1. Launch EvMoto User app (Dev Golang) and configure pickup and destination points
+2. Select EvRide Electric service option and confirm payment method (EvWallet / Cash)
+3. Tap 'Book EvMoto' and wait 3-5s until app transitions to 'Searching Driver' state
+4. Driver account (85156125633, OTP: 1234) receives trip ping on Dev Driver APK and taps 'Accept Order'
+5. Driver navigates to pickup point, communicates via in-trip Chat/Photo, and starts trip
+6. Driver completes trip with 'Cash Collected' / Paid status with 3-5s buffer delay
+7. User receives trip completion popup dialog and submits 5-star rating</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Status staging 100% konsisten dan siap digunakan untuk live testing.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/docs/reports/Test_Cases_EvMoto_Mobile_EN.xlsx
+++ b/docs/reports/Test_Cases_EvMoto_Mobile_EN.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User'!$A$1:$I$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Driver'!$A$1:$I$349</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Admin Dashboard'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14310,6 +14310,406 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId327"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>328</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="328" name="Image 328" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId328"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>329</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="329" name="Image 329" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId329"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>330</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="330" name="Image 330" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId330"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>331</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="331" name="Image 331" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId331"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>332</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="332" name="Image 332" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId332"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>333</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="333" name="Image 333" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId333"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>334</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="334" name="Image 334" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId334"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>335</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="335" name="Image 335" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId335"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>336</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="336" name="Image 336" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId336"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>337</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="337" name="Image 337" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId337"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>338</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="338" name="Image 338" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId338"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>339</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="339" name="Image 339" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId339"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>340</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="340" name="Image 340" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId340"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>341</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="341" name="Image 341" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId341"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>342</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="342" name="Image 342" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId342"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>343</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="742950" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="343" name="Image 343" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId343"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -25819,7 +26219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -39249,8 +39649,931 @@
         </is>
       </c>
     </row>
+    <row r="329" ht="135" customHeight="1">
+      <c r="A329" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PT_01</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr"/>
+      <c r="C329" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D329" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E329" s="8" t="inlineStr">
+        <is>
+          <t>1. Terdapat Order reguler baru ORD-SIMULTAN-01 dan 5 driver standby di Ring 1 (&lt; 5 KM)
+2. Sistem menyiarkan batch order ke seluruh driver di Ring 1
+3. Kelima driver Ring 1 Accept popup order secara simultan
+4. Driver DRV-06 dan DRV-07 di Ring 2 (&gt; 5 KM) belum Accept popup order
+5. Driver DRV-03 melakukan Swipe Terima pada Order ORD-SIMULTAN-01
+6. Popup order pada DRV-01, DRV-02, DRV-04, dan DRV-05 SEKETIKA DICABUT (HILANG)</t>
+        </is>
+      </c>
+      <c r="F329" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Kelima driver Ring 1 Accept popup order secara bersamaan. - Saat DRV-03 Accept order, popup di DRV-01, DRV-02, DRV-04, dan DRV-05 LANGSUNG HILANG!</t>
+        </is>
+      </c>
+      <c r="G329" s="10" t="inlineStr"/>
+      <c r="H329" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I329" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="135" customHeight="1">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PT_02</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr"/>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>1. Customer membuat Order Advance Booking ORD-ADV-99 (Jarak 8.5 KM, Tarif Rp 65.000)
+2. Sistem mendispatch batch Advance Booking ke Ring 1
+3. Driver DRV-01 melakukan Swipe Terima pada Order Advance Booking
+4. Popup Advance Booking pada DRV-02 hingga DRV-05 langsung hilang</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="inlineStr">
+        <is>
+          <t>Instant revocation dan pemisahan tipe 'advance' bekerja presisi.</t>
+        </is>
+      </c>
+      <c r="G330" s="5" t="inlineStr"/>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I330" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="135" customHeight="1">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PF_01</t>
+        </is>
+      </c>
+      <c r="B331" s="8" t="inlineStr"/>
+      <c r="C331" s="9" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D331" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E331" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-REJECT-01 disiarkan ke 5 driver Ring 1
+2. Driver DRV-01 Reject (Reject) tawaran tersebut
+3. Order tidak mati, melainkan berstatus RE_DISPATCHING
+4. Popup order DICABUT dari DRV-01 dan DRV-01 di-blacklist
+5. Order TETAP MUNCUL dan aktif pada driver rekanan di Ring 1 (DRV-02, DRV-03, DRV-04, DRV-05)
+6. Driver DRV-02 kemudian mengambil (Accept) order tersebut</t>
+        </is>
+      </c>
+      <c r="F331" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Order ORD-REJECT-01 TIDAK BOLEH CANCELLED (harus tetap aktif RE_DISPATCHING). - DRV-01 masuk ke daftar Blacklist sehingga order tersebut TIDAK AKAN PERNAH muncul lagi di DRV-01. - Order tetap Displayed dan siap diambil oleh Driver DRV-02, DRV-03, DRV-04, dan DRV-05.</t>
+        </is>
+      </c>
+      <c r="G331" s="10" t="inlineStr"/>
+      <c r="H331" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I331" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="135" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_PF_02</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr"/>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Positive False</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-CHAIN-01 disiarkan ke 5 driver Ring 1
+2. DRV-01, DRV-02, dan DRV-03 berturut-turut Reject order
+3. DRV-01, DRV-02, dan DRV-03 semuanya masuk blacklist dan tidak melihat order
+4. DRV-04 dan DRV-05 masih memiliki popup order aktif di Screen mereka
+5. DRV-05 akhirnya melakukan Swipe Terima</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="inlineStr">
+        <is>
+          <t>Order tetap bertahan di pool, driver 1-3 tidak Accept lagi, sedangkan Driver 4 &amp; Driver 5 masih dapat melihat dan mengambil order.</t>
+        </is>
+      </c>
+      <c r="G332" s="5" t="inlineStr"/>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I332" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="135" customHeight="1">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NT_01</t>
+        </is>
+      </c>
+      <c r="B333" s="8" t="inlineStr"/>
+      <c r="C333" s="9" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D333" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-EXPAND-01 disiarkan ke 5 driver Ring 1
+2. Kelima driver Ring 1 (DRV-01 s/d DRV-05) Reject Order secara berurutan
+3. Sistem mendeteksi Ring 1 habis dan memicu Distance Band Expansion ke Ring 2
+4. Order secara otomatis muncul di Screen DRV-06 dan DRV-07 (Ring 2 &gt; 5 KM)
+5. Seluruh driver Ring 1 (DRV-01 s/d DRV-05) tetap bersih tanpa popup
+6. Driver DRV-06 di Ring 2 Accept Order tersebut</t>
+        </is>
+      </c>
+      <c r="F333" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Sistem otomatis mengaktifkan ekspansi radius Distance Band (Ring 2 &gt; 5 KM). - Popup order baru seketika muncul di Driver DRV-06 dan DRV-07. - Driver 1–5 di Ring 1 tidak mendapatkan order tersebut lagi.</t>
+        </is>
+      </c>
+      <c r="G333" s="10" t="inlineStr"/>
+      <c r="H333" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I333" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="135" customHeight="1">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NT_02</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr"/>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Negative True</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-EXHAUST-01 diproses
+2. Kedua driver Ring 2 (DRV-06 dan DRV-07) juga Reject Order
+3. Sistem secara aman beralih ke status NO_DRIVER_FOUND</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>Sistem mencapai status 'NO_DRIVER_FOUND' secara graceful tanpa exception atau memory leak.</t>
+        </is>
+      </c>
+      <c r="G334" s="5" t="inlineStr"/>
+      <c r="H334" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I334" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="135" customHeight="1">
+      <c r="A335" s="7" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NF_01</t>
+        </is>
+      </c>
+      <c r="B335" s="8" t="inlineStr"/>
+      <c r="C335" s="9" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D335" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E335" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-POST-CANCEL-01 diterima oleh Driver DRV-01
+2. Driver DRV-01 membatalkan Order karena 'Ban Bocor / Kendala Kendaraan'
+3. Order tidak mati, melainkan berstatus RE_DISPATCHING
+4. Order secara otomatis muncul kembali di Screen rekanan (DRV-02, DRV-03, DRV-04, DRV-05)
+5. Driver DRV-01 yang membatalkan TIDAK melihat order tersebut lagi (Blacklisted)
+6. Driver DRV-04 mengambil alih Order yang dibatalkan DRV-01
+7. Popup seketika hilang dari DRV-02, DRV-03, dan DRV-05</t>
+        </is>
+      </c>
+      <c r="F335" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - CRUCIAL FIX: Order TIDAK DIBATALKAN KE CUSTOMER! - Status order kembali ke RE_DISPATCHING. - DRV-01 kembali standby dan di-blacklist dari order tersebut. - Order otomatis di-reassign ke sisa rekan standby di Ring 1 (DRV-02 s/d DRV-05).</t>
+        </is>
+      </c>
+      <c r="G335" s="10" t="inlineStr"/>
+      <c r="H335" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I335" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="135" customHeight="1">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>TC_CASCADE_NF_02</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr"/>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-88 disiarkan ke Ring 1
+2. DRV-02 dan DRV-03 mencoba Accept order secara simultan
+3. Tepat 1 driver memenangkan order dan driver kedua mendapatkan notifikasi aman</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="inlineStr">
+        <is>
+          <t>Tepat 1 driver sukses Accept order; driver kedua ditolak dengan aman tanpa crash.</t>
+        </is>
+      </c>
+      <c r="G336" s="5" t="inlineStr"/>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I336" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="135" customHeight="1">
+      <c r="A337" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_01</t>
+        </is>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Dua Perangkat Driver Melakukan Swipe Bersamaan &amp; Verify Revokasi Modal.</t>
+        </is>
+      </c>
+      <c r="C337" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D337" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E337" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-01 disiarkan ke Perangkat Driver 1 dan Driver 2
+2. Driver 1 dan Driver 2 melakukan swipe simultan
+3. Screen Driver 1 menampilkan status Aktif, Screen Driver 2 tertutup modalnya</t>
+        </is>
+      </c>
+      <c r="F337" s="8" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G337" s="10" t="inlineStr"/>
+      <c r="H337" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I337" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="135" customHeight="1">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_02</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Driver Pemenang Membatalkan Order -&gt; Driver Kalah Wajib Muncul Pop-up Kembali.</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>1. Driver 1 menang dan Driver 2 kalah swipe pada ORD-VIS-02
+2. Driver 1 membatalkan order
+3. Pada Driver 2, Pop-up Modal KARTU ORDER WAJIB MUNCUL KEMBALI DI Screen</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G338" s="5" t="inlineStr"/>
+      <c r="H338" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I338" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="135" customHeight="1">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_03</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Alur Visual 3 Perangkat: Driver 1 Accept -&gt; Driver 1 Cancel -&gt; Driver 2 Reject -&gt; Driver 3 Accept.</t>
+        </is>
+      </c>
+      <c r="C339" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D339" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E339" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-03 disiarkan ke Driver 1, 2, dan 3</t>
+        </is>
+      </c>
+      <c r="F339" s="8" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G339" s="10" t="inlineStr"/>
+      <c r="H339" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I339" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="135" customHeight="1">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_04</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Seluruh Modal Kartu Order Terverifikasi TIDAK Memiliki Elemen Countdown Timer.</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>1. Order disiarkan ke 5 perangkat pengemudi di Ring 1</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G340" s="5" t="inlineStr"/>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I340" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="135" customHeight="1">
+      <c r="A341" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_05</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Perangkat Driver yang Sedang Mengantar (Busy) atau Offline Tidak Boleh Menampilkan Pop-up.</t>
+        </is>
+      </c>
+      <c r="C341" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D341" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E341" s="8" t="inlineStr">
+        <is>
+          <t>1. Driver 1 sedang offline dan Driver 2 sedang dalam perjalanan (busy)
+2. Order ORD-VIS-05 disiarkan
+3. Driver 1 dan 2 tidak Accept popup, sedangkan Driver 3, 4, 5 tetap Accept</t>
+        </is>
+      </c>
+      <c r="F341" s="8" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G341" s="10" t="inlineStr"/>
+      <c r="H341" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I341" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="135" customHeight="1">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_06</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Transisi Visual Pop-up dari Ring 1 ke Ring 2 saat Driver Dekat Reject.</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-06 dibuat
+2. Pop-up berpindah ke Screen perangkat Driver 6 dan Driver 7 di Ring 2</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G342" s="5" t="inlineStr"/>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I342" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="135" customHeight="1">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>TC_VIS_07</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Kartu Order Terjadwal Menampilkan Badge 'ADVANCE BOOKING' secara Eksplisit.</t>
+        </is>
+      </c>
+      <c r="C343" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="inlineStr">
+        <is>
+          <t>1. Order Advance Booking ORD-VIS-07</t>
+        </is>
+      </c>
+      <c r="F343" s="8" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G343" s="10" t="inlineStr"/>
+      <c r="H343" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I343" s="8" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="135" customHeight="1">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>TC_VIS_08</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Sinkronisasi Status Bar Notification Tray dengan In-App Screen Modal.</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>User is on the active application screen</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-VIS-08 disiarkan</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>System responds successfully, valid data is processed, and UI transitions to the expected state without issues.</t>
+        </is>
+      </c>
+      <c r="G344" s="5" t="inlineStr"/>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I344" s="3" t="inlineStr">
+        <is>
+          <t>Stable feature. No anomalies or bugs detected on this Android build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="135" customHeight="1">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>REPRODUCE_BUG_01_DRIVER_REJECT_PREMATURE_ORDER_CANCELLATION</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr"/>
+      <c r="C345" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-BUG-01 disiarkan serentak ke 5 driver di Ring 1 (&lt; 5 KM)
+2. [BUG CONFIRMED] Order mati total (CANCELLED) dan Driver 2 s/d 5 TIDAK PERNAH Accept order!
+3. [PATCHED LOGIC] Menguji alur perbaikan arsitektur baru...
+4. [FIX VERIFIED] Order berstatus RE_DISPATCHING, Driver 1 di-blacklist, dan Driver 2 s/d 5 TETAP melihat order!</t>
+        </is>
+      </c>
+      <c r="F345" s="8" t="inlineStr">
+        <is>
+          <t>System synchronously processes order between User and Driver without race conditions, map route is accurate, and ride status updates in realtime.</t>
+        </is>
+      </c>
+      <c r="G345" s="10" t="inlineStr">
+        <is>
+          <t>[Evidence Attached]</t>
+        </is>
+      </c>
+      <c r="H345" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I345" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="135" customHeight="1">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>REPRODUCE_BUG_02_SIMULTANEOUS_ACCEPTANCE_RACE_CONDITION</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr"/>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>Negative False</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-RACE-02 disiarkan ke Ring 1
+2. [BUG #2 CONFIRMED &amp; SAFELY CONTAINED BY ATOMIC LOCK]</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr">
+        <is>
+          <t>System sanitizes chat/notes input (SQLi/XSS) and dampens aggressive multi-tapping; application remains stable without crashing.</t>
+        </is>
+      </c>
+      <c r="G346" s="5" t="inlineStr">
+        <is>
+          <t>[Evidence Attached]</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I346" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="135" customHeight="1">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>REPRODUCE_BUG_03_DELAYED_PEER_REVOCATION_STALE_POPUP</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr"/>
+      <c r="C347" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>1. Order ORD-STALE-03 disiarkan ke Driver 1 hingga 5</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr">
+        <is>
+          <t>System synchronously processes order between User and Driver without race conditions, map route is accurate, and ride status updates in realtime.</t>
+        </is>
+      </c>
+      <c r="G347" s="10" t="inlineStr">
+        <is>
+          <t>[Evidence Attached]</t>
+        </is>
+      </c>
+      <c r="H347" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I347" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="135" customHeight="1">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>REPRODUCE_BUG_04_DISTANCE_BAND_EXPANSION_STALLING_ON_RING_EXHAUSTION</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr"/>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>1. Order ORD-STALL-04 disiarkan ke Ring 1
+2. 4 Driver pertama Reject order
+3. Driver ke-5 (terakhir di Ring 1) Reject order
+4. [BUG-04 REPRODUCED &amp; SOLVED] Sistem wajib Early Band Shift ke Ring 2 tanpa stalling!
+5. Order secara otomatis langsung muncul di Driver 6 dan Driver 7 (&gt; 5 KM)</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>System synchronously processes order between User and Driver without race conditions, map route is accurate, and ride status updates in realtime.</t>
+        </is>
+      </c>
+      <c r="G348" s="5" t="inlineStr">
+        <is>
+          <t>[Evidence Attached]</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I348" s="3" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="135" customHeight="1">
+      <c r="A349" s="7" t="inlineStr">
+        <is>
+          <t>REPRODUCE_BUG_05_SIMULTANEOUS_SWIPE_WINNER_CANCEL_LOSER_RECEIVES_NOTIF_ONLY_NO_POPUP</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr"/>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>Positive True</t>
+        </is>
+      </c>
+      <c r="D349" s="8" t="inlineStr">
+        <is>
+          <t>EvMoto User &amp; Driver apps active on Dev Golang environment (https://evmotodev.justkidding.app). User: 82146625856 / OTP 1234. Driver: 85156125633 / OTP Bypass 1234 (evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk). 3-5s pacing buffer active.</t>
+        </is>
+      </c>
+      <c r="E349" s="8" t="inlineStr">
+        <is>
+          <t>1. Kondisi 1 Customer dan 2 Driver Online Standby (DRV-01 dan DRV-02)
+2. Driver 1 dan Driver 2 melakukan Swipe Terima secara bersamaan (Simultaneous Swipe)
+3. Driver 1 membatalkan order yang baru saja dimenangkan
+4. [BUG #5 CONFIRMED] Ponsel Driver 2 Accept Push Notif/Suara, TETAPI POPUP KARTU ORDER TIDAK MUNCUL DI Screen!
+5. [PATCHED VALIDATION] Menguji perbaikan UI lifecycle pada Driver 2...
+6. [PATCH VERIFIED] Pada versi perbaikan, Pop-up Modal KEMBALI MUNCUL dan Driver 2 BISA SWIPE!</t>
+        </is>
+      </c>
+      <c r="F349" s="8" t="inlineStr">
+        <is>
+          <t>System synchronously processes order between User and Driver without race conditions, map route is accurate, and ride status updates in realtime.</t>
+        </is>
+      </c>
+      <c r="G349" s="10" t="inlineStr">
+        <is>
+          <t>[Evidence Attached]</t>
+        </is>
+      </c>
+      <c r="H349" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I349" s="8" t="inlineStr">
+        <is>
+          <t>Driver Role Validated: APK evmoto-driver-1.9.27-env-dev_golang-20261020-v7a.apk, Driver Account 85156125633, OTP Bypass 1234. Backend Dev Golang (https://evmotodev.justkidding.app). Pacing delay 3-5 seconds applied to mitigate race conditions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I328"/>
+  <autoFilter ref="A1:I349"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
